--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3260-223-CM25</t>
+          <t>3712-102-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1674.33</v>
+        <v>6460.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2711-555-CM25</t>
+          <t>3260-223-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>21548.04</v>
+        <v>1674.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5416-1478-CM25</t>
+          <t>2711-555-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NextTime Software S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>99.576.370-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1486.91</v>
+        <v>21548.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5416-1524-CM25</t>
+          <t>5416-1478-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NextTime Software S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>99.576.370-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1691.61</v>
+        <v>1486.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3712-1170-CM25</t>
+          <t>5416-1524-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>56773.89</v>
+        <v>1691.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2450-1038-CM25</t>
+          <t>3712-1170-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>31062.61</v>
+        <v>56773.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3712-4-CM26</t>
+          <t>2450-1038-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11721.74</v>
+        <v>31062.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3872-43-CM26</t>
+          <t>3712-4-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1523.2</v>
+        <v>11721.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4247-154-CM26</t>
+          <t>3872-43-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13305.39</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3713-38-CM26</t>
+          <t>4247-154-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2958.82</v>
+        <v>13305.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1491370-19-CM26</t>
+          <t>3713-38-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Proyecto ING2530001 DECANAT FACULTAD DE INGENIERÍA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INFO WORLD SA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.532.020-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>768.23</v>
+        <v>2958.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3707-206-CM26</t>
+          <t>1491370-19-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>Proyecto ING2530001 DECANAT FACULTAD DE INGENIERÍA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>INFO WORLD SA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.532.020-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>13393.95</v>
+        <v>768.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1276532-11-CM26</t>
+          <t>3707-206-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.892.100-9</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Administración Central</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10119.15</v>
+        <v>13393.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3712-291-CM26</t>
+          <t>1276532-11-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>Administración Central</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11718.64</v>
+        <v>10119.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3884-203-CM26</t>
+          <t>3712-291-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11805.99</v>
+        <v>11718.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1057439-3171-CM26</t>
+          <t>3884-203-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1596.98</v>
+        <v>11805.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>624-74-CM26</t>
+          <t>1057439-3171-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>70089.22</v>
+        <v>1596.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2450-536-CM26</t>
+          <t>624-74-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>33398.14</v>
+        <v>70089.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>527481-51-CM26</t>
+          <t>2450-536-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13305.39</v>
+        <v>33398.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3616-82-CM26</t>
+          <t>527481-51-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1728,6 +1728,67 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
+        <v>13305.39</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3616-82-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>6238.42</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3712-102-CM25</t>
+          <t>1057439-799-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6460.18</v>
+        <v>6556.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3260-223-CM25</t>
+          <t>3712-102-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1674.33</v>
+        <v>6460.18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2711-555-CM25</t>
+          <t>2450-183-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>21548.04</v>
+        <v>27602.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5416-1478-CM25</t>
+          <t>1057439-12720-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NextTime Software S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>99.576.370-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1486.91</v>
+        <v>1780.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5416-1524-CM25</t>
+          <t>624-62-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1691.61</v>
+        <v>57080.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3712-1170-CM25</t>
+          <t>1276532-12-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>56773.89</v>
+        <v>9506.860000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2450-1038-CM25</t>
+          <t>745915-32-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>31062.61</v>
+        <v>12509.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3712-4-CM26</t>
+          <t>750301-50-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11721.74</v>
+        <v>13302.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3872-43-CM26</t>
+          <t>3707-213-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1523.2</v>
+        <v>13393.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4247-154-CM26</t>
+          <t>3712-398-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>13305.39</v>
+        <v>5872.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3713-38-CM26</t>
+          <t>1057439-13532-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2958.82</v>
+        <v>46532.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1491370-19-CM26</t>
+          <t>527481-55-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Proyecto ING2530001 DECANAT FACULTAD DE INGENIERÍA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INFO WORLD SA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.532.020-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>768.23</v>
+        <v>13316.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3707-206-CM26</t>
+          <t>3616-92-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>13393.95</v>
+        <v>6970.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1276532-11-CM26</t>
+          <t>624-158-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.892.100-9</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Administración Central</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10119.15</v>
+        <v>1521.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3712-291-CM26</t>
+          <t>3884-411-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11718.64</v>
+        <v>11097.63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3884-203-CM26</t>
+          <t>3712-683-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11805.99</v>
+        <v>854.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057439-3171-CM26</t>
+          <t>3265-1941-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1596.98</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>624-74-CM26</t>
+          <t>624-247-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>70089.22</v>
+        <v>14283.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2450-536-CM26</t>
+          <t>2446-1601-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,28 +1652,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>33398.14</v>
+        <v>806820</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>527481-51-CM26</t>
+          <t>3260-223-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1687,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13305.39</v>
+        <v>1674.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3616-82-CM26</t>
+          <t>2711-555-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1748,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,7 +1793,1166 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
+        <v>21548.04</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5416-1478-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NextTime Software S.A.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>99.576.370-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>1486.91</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5416-1524-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1691.61</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3712-1170-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>56773.89</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2450-1038-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>31062.61</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3712-4-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>11721.74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3872-43-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.040.900-3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1523.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4247-154-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.040.900-3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>13305.39</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3713-38-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>2958.82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1491370-19-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Proyecto ING2530001 DECANAT FACULTAD DE INGENIERÍA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>INFO WORLD SA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.532.020-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>768.23</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3707-206-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.040.200-9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>13393.95</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1276532-11-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>70.892.100-9</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Administración Central</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>10119.15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3712-291-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>11718.64</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3884-203-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.040.600-4</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>11805.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1057439-3171-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NETSUS SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1596.98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>624-74-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>70089.22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2450-536-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>33398.14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>527481-51-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>13305.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3616-82-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
         <v>6238.42</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>624-187-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>7868.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Proyecto ING2530001 DECANAT FACULTAD DE INGENIERÍA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Administración Central</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
@@ -562,7 +562,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1854,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1980,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2045,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2110,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2175,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2240,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2305,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2370,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2496,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2561,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2626,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2691,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2756,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2821,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2886,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2951,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3016,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3081,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1276532-12-CM25</t>
+          <t>745915-32-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9506.860000000001</v>
+        <v>12509.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>745915-32-CM25</t>
+          <t>750301-50-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12509.14</v>
+        <v>13302.96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>750301-50-CM25</t>
+          <t>1276532-12-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13302.96</v>
+        <v>9506.860000000001</v>
       </c>
     </row>
     <row r="10">
@@ -3093,6 +3093,136 @@
       </c>
       <c r="M41" s="2" t="n">
         <v>7868.52</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1305532-101-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>18445</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4295-88-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>388312.61</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/coquimbo.xlsx
@@ -3053,7 +3053,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
